--- a/data/samples/cold_storage_status.xlsx
+++ b/data/samples/cold_storage_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,15 +424,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>cold_storage_total_capacity_qty</t>
+          <t>total_capacity_qty</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>cold_storage_current_qty</t>
+          <t>current_occupied_qty</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
+        <is>
+          <t>expected_inbound_qty</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>expected_outbound_qty</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>warning_threshold_qty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>projected_occupied_qty</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>remaining_capacity_qty</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -450,7 +480,25 @@
       <c r="C2" t="n">
         <v>120</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G2" t="n">
+        <v>120</v>
+      </c>
+      <c r="H2" t="n">
+        <v>380</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>default sample</t>
         </is>
